--- a/daily_matches/job_matches_2026-09-27.xlsx
+++ b/daily_matches/job_matches_2026-09-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Front End Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, S3, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, RAG, Copilot, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d8f8c4202abcea</t>
+          <t>https://www.indeed.com/viewjob?jk=d74f91161f0786df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, Spark, Kafka, SQL, Snowflake, Databricks, GenAI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Data Scientist, RAG, Copilot, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d55a501fc68d234</t>
+          <t>https://www.indeed.com/viewjob?jk=94e06db5919f7704</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-Software Engineer III</t>
+          <t>Full-stack Engineer 5 (AI Platform &amp; Knowledge Library) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,252 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9960bbb7b643cd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Engineer - Spatial Analytics</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Community Transit</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Everett, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b39d8b03c9097b</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=749fcfc1e9033aea</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, AKS, CI/CD, Git, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1d1a332b4190af</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63477b57445fa63f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bravent LLC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, AKS, CI/CD, Git, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6920cb754983354d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Healthcare Data Analyst, Analytics Hub</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ECG Management Consultants</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab8f798fcade81</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Operations Research Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>University of Phoenix</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Redshift, Redshift, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92735ce11d07b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c9d136b2b0b4aee</t>
         </is>
       </c>
     </row>
